--- a/data_plan.xlsx
+++ b/data_plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\MATH4100-DS\datascience-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C573A21D-8608-495E-8453-67108A8EC056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4806BE67-D866-4CE9-9FE1-4B2E29A3B723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{84021EAC-F933-478D-95E5-945724B0C9EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84021EAC-F933-478D-95E5-945724B0C9EB}"/>
   </bookViews>
   <sheets>
     <sheet name="ut_bills" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="174">
   <si>
     <t>bill_id</t>
   </si>
@@ -215,9 +215,6 @@
     <t>0-9</t>
   </si>
   <si>
-    <t>Number of substitutes to the bill</t>
-  </si>
-  <si>
     <t>Name of representative/senator, title abbrv. last, first</t>
   </si>
   <si>
@@ -281,9 +278,6 @@
     <t>2026GS</t>
   </si>
   <si>
-    <t>Session id; general session, special sessions (usually first-second)</t>
-  </si>
-  <si>
     <t>characters(HB0001S01: Rep. Wilcox, Ryan)</t>
   </si>
   <si>
@@ -482,13 +476,88 @@
     <t>might not be worth using without subject def (are subjs enrolled or og)</t>
   </si>
   <si>
-    <t>might want to make only GS; check to see how many bills we'd lose</t>
-  </si>
-  <si>
     <t>IF TIME ALLOWS: split committees one-hot dummy</t>
   </si>
   <si>
     <t>NOTE: not every bill came out of committee          CLEAN: change NAs to 'No committee'                      CLEAN: make 'came out of committee' variable</t>
+  </si>
+  <si>
+    <t>Availablity</t>
+  </si>
+  <si>
+    <t>wrong until 2025</t>
+  </si>
+  <si>
+    <t>derived (2016-2025), original (2025-206)</t>
+  </si>
+  <si>
+    <t>committee1</t>
+  </si>
+  <si>
+    <t>If the bill came out of committee; 1 if yes, 0 no</t>
+  </si>
+  <si>
+    <t>cospon1</t>
+  </si>
+  <si>
+    <t>If the bill had cosponsors</t>
+  </si>
+  <si>
+    <t>floorspon1</t>
+  </si>
+  <si>
+    <t>If the bill had a floor sponsor</t>
+  </si>
+  <si>
+    <t>cospon_num</t>
+  </si>
+  <si>
+    <t>Number of cosponsors the bill had</t>
+  </si>
+  <si>
+    <t>The more cosponsors, the more support there was</t>
+  </si>
+  <si>
+    <t>num_sub_new</t>
+  </si>
+  <si>
+    <t>Derived number of substitutes based on the substitute # of the active/enrolled bill</t>
+  </si>
+  <si>
+    <t>Not the best for regression; may measure "a substitute was passed" instead of "how many substitutes did it have". BUT applies to all years instead of 2025 and on.</t>
+  </si>
+  <si>
+    <t>money1</t>
+  </si>
+  <si>
+    <t>money_sum</t>
+  </si>
+  <si>
+    <t>If the bill had money appropriated</t>
+  </si>
+  <si>
+    <t>0-67</t>
+  </si>
+  <si>
+    <t>0-2324459900</t>
+  </si>
+  <si>
+    <t>Total amount of money appropriated in the bill (in $ amounts)</t>
+  </si>
+  <si>
+    <t>CLEAN: need to adjust values for inflation</t>
+  </si>
+  <si>
+    <t>Session id on website</t>
+  </si>
+  <si>
+    <t>Number of substitutes to the bill (2025 and 2026)</t>
+  </si>
+  <si>
+    <t>CLEAN: need to pull sub # from active version; reduces use value tho (wanted to see if # of subs affects passage)                                                  EXPLOR: From 2025 on, only 52 bills (5%) have different enrolled substitute and number of subs</t>
+  </si>
+  <si>
+    <t>Might not be powerful enough</t>
   </si>
 </sst>
 </file>
@@ -516,7 +585,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -526,12 +595,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,20 +611,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -891,27 +984,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07347EA0-385C-4B0A-8BAB-822EDDEC5A8B}">
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" customWidth="1"/>
-    <col min="5" max="5" width="39.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="51.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.88671875" customWidth="1"/>
+    <col min="6" max="6" width="39.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="53.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="51.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -922,31 +1015,34 @@
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>69</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -956,20 +1052,20 @@
       <c r="C4" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>44</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -979,17 +1075,20 @@
       <c r="C5" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>49</v>
       </c>
       <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -997,22 +1096,22 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G6" t="s">
+      <c r="F6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="I6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
@@ -1020,25 +1119,28 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7">
+        <v>2023</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F7" t="s">
-        <v>85</v>
-      </c>
       <c r="G7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I7" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
@@ -1046,28 +1148,28 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F8" t="s">
-        <v>85</v>
-      </c>
       <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1077,20 +1179,20 @@
       <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="G9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1103,17 +1205,17 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F10" t="s">
-        <v>85</v>
-      </c>
       <c r="G10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1123,18 +1225,18 @@
       <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F11" t="s">
-        <v>85</v>
-      </c>
       <c r="G11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B12" t="s">
@@ -1143,17 +1245,26 @@
       <c r="C12" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" t="s">
-        <v>131</v>
+      <c r="E12" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="H12" t="s">
+        <v>150</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1161,25 +1272,28 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13">
+        <v>2023</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D13" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J13" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1187,19 +1301,19 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G14" t="s">
+      <c r="F14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J14" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1207,48 +1321,48 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="J15" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
       </c>
       <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F16" t="s">
-        <v>85</v>
-      </c>
       <c r="G16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="I16" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -1259,19 +1373,19 @@
         <v>25</v>
       </c>
       <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D17" t="s">
+      <c r="H17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -1282,12 +1396,12 @@
         <v>25</v>
       </c>
       <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1299,19 +1413,19 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s">
+        <v>138</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>144</v>
+      <c r="I19" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1324,34 +1438,34 @@
       <c r="C20" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
       <c r="C21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>44</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>18</v>
       </c>
@@ -1359,19 +1473,16 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="G22" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" t="s">
         <v>30</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -1384,19 +1495,19 @@
       <c r="C23" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>41</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
@@ -1404,42 +1515,42 @@
       <c r="C24" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>41</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
         <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F25" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="G25" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>132</v>
+        <v>83</v>
+      </c>
+      <c r="H25" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
@@ -1447,19 +1558,19 @@
       <c r="C26" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F26" t="s">
-        <v>131</v>
+      <c r="F26" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="G26" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
@@ -1467,19 +1578,19 @@
       <c r="C27" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F27" t="s">
-        <v>131</v>
+      <c r="F27" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="G27" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
@@ -1487,19 +1598,19 @@
       <c r="C28" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" t="s">
-        <v>131</v>
+      <c r="F28" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G28" t="s">
+        <v>129</v>
+      </c>
+      <c r="H28" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
         <v>26</v>
@@ -1507,19 +1618,19 @@
       <c r="C29" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F29" t="s">
-        <v>131</v>
+      <c r="F29" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="G29" t="s">
+        <v>129</v>
+      </c>
+      <c r="H29" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B30" t="s">
         <v>26</v>
@@ -1527,19 +1638,19 @@
       <c r="C30" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F30" t="s">
-        <v>131</v>
+      <c r="F30" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="G30" t="s">
+        <v>129</v>
+      </c>
+      <c r="H30" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
         <v>26</v>
@@ -1547,19 +1658,19 @@
       <c r="C31" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F31" t="s">
-        <v>131</v>
+      <c r="F31" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="G31" t="s">
+        <v>129</v>
+      </c>
+      <c r="H31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
@@ -1567,298 +1678,461 @@
       <c r="C32" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F32" t="s">
-        <v>131</v>
+      <c r="F32" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="G32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="H32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G33" t="s">
+        <v>129</v>
+      </c>
+      <c r="H33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" t="s">
+        <v>129</v>
+      </c>
+      <c r="H34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>95</v>
       </c>
-      <c r="B33" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F33" t="s">
-        <v>131</v>
-      </c>
-      <c r="G33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="G35" t="s">
+        <v>129</v>
+      </c>
+      <c r="H35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>96</v>
       </c>
-      <c r="B34" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F34" t="s">
-        <v>131</v>
-      </c>
-      <c r="G34" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="G36" t="s">
+        <v>129</v>
+      </c>
+      <c r="H36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>97</v>
       </c>
-      <c r="B35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" t="s">
-        <v>33</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F35" t="s">
-        <v>131</v>
-      </c>
-      <c r="G35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="G37" t="s">
+        <v>129</v>
+      </c>
+      <c r="H37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>98</v>
       </c>
-      <c r="B36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>33</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F36" t="s">
-        <v>131</v>
-      </c>
-      <c r="G36" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="G38" t="s">
+        <v>129</v>
+      </c>
+      <c r="H38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>99</v>
       </c>
-      <c r="B37" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F37" t="s">
-        <v>131</v>
-      </c>
-      <c r="G37" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="G39" t="s">
+        <v>129</v>
+      </c>
+      <c r="H39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>100</v>
       </c>
-      <c r="B38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" t="s">
-        <v>33</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F38" t="s">
-        <v>131</v>
-      </c>
-      <c r="G38" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="G40" t="s">
+        <v>129</v>
+      </c>
+      <c r="H40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>101</v>
       </c>
-      <c r="B39" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" t="s">
-        <v>33</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>33</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F39" t="s">
-        <v>131</v>
-      </c>
-      <c r="G39" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="G41" t="s">
+        <v>129</v>
+      </c>
+      <c r="H41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>102</v>
       </c>
-      <c r="B40" t="s">
-        <v>26</v>
-      </c>
-      <c r="C40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E40" s="1" t="s">
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F40" t="s">
-        <v>131</v>
-      </c>
-      <c r="G40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="G42" t="s">
+        <v>129</v>
+      </c>
+      <c r="H42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>103</v>
       </c>
-      <c r="B41" t="s">
-        <v>26</v>
-      </c>
-      <c r="C41" t="s">
-        <v>33</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>33</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F41" t="s">
-        <v>131</v>
-      </c>
-      <c r="G41" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="G43" t="s">
+        <v>129</v>
+      </c>
+      <c r="H43" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>104</v>
       </c>
-      <c r="B42" t="s">
-        <v>26</v>
-      </c>
-      <c r="C42" t="s">
-        <v>33</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F42" t="s">
-        <v>131</v>
-      </c>
-      <c r="G42" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="G44" t="s">
+        <v>129</v>
+      </c>
+      <c r="H44" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>105</v>
       </c>
-      <c r="B43" t="s">
-        <v>26</v>
-      </c>
-      <c r="C43" t="s">
-        <v>33</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s">
+        <v>33</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F43" t="s">
-        <v>131</v>
-      </c>
-      <c r="G43" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="G45" t="s">
+        <v>129</v>
+      </c>
+      <c r="H45" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>106</v>
       </c>
-      <c r="B44" t="s">
-        <v>26</v>
-      </c>
-      <c r="C44" t="s">
-        <v>33</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F44" t="s">
-        <v>131</v>
-      </c>
-      <c r="G44" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45" t="s">
-        <v>26</v>
-      </c>
-      <c r="C45" t="s">
-        <v>33</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F45" t="s">
-        <v>131</v>
-      </c>
-      <c r="G45" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>108</v>
-      </c>
-      <c r="B46" t="s">
-        <v>26</v>
-      </c>
-      <c r="C46" t="s">
-        <v>33</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F46" t="s">
-        <v>131</v>
-      </c>
       <c r="G46" t="s">
-        <v>31</v>
+        <v>129</v>
+      </c>
+      <c r="H46" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>151</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G47" t="s">
+        <v>129</v>
+      </c>
+      <c r="H47" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48">
+        <v>2023</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G48" t="s">
+        <v>129</v>
+      </c>
+      <c r="H48" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>155</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G49" t="s">
+        <v>129</v>
+      </c>
+      <c r="H49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>163</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G50" t="s">
+        <v>129</v>
+      </c>
+      <c r="H50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>157</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E51">
+        <v>2023</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G51" t="s">
+        <v>129</v>
+      </c>
+      <c r="H51" t="s">
+        <v>31</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>160</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52">
+        <v>2016</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G52" t="s">
+        <v>129</v>
+      </c>
+      <c r="H52" t="s">
+        <v>31</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" t="s">
+        <v>167</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G53" t="s">
+        <v>129</v>
+      </c>
+      <c r="H53" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Covariate"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Outcome"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>